--- a/docs/hub/estate/Planning and Insight/Working/Awarding gap/HE awarding gap extract WORKING FINAL.xlsx
+++ b/docs/hub/estate/Planning and Insight/Working/Awarding gap/HE awarding gap extract WORKING FINAL.xlsx
@@ -525,16 +525,16 @@
         <v>1049</v>
       </c>
       <c r="B2" t="n">
-        <v>78</v>
+        <v>884</v>
       </c>
       <c r="C2" t="n">
-        <v>83.3</v>
+        <v>61.5</v>
       </c>
       <c r="D2" t="n">
-        <v>54.8</v>
+        <v>36.5</v>
       </c>
       <c r="E2" t="n">
-        <v>28.6</v>
+        <v>24.9</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -547,16 +547,16 @@
         <v>1050</v>
       </c>
       <c r="B3" t="n">
-        <v>127</v>
+        <v>948</v>
       </c>
       <c r="C3" t="n">
-        <v>67.3</v>
+        <v>59.1</v>
       </c>
       <c r="D3" t="n">
-        <v>44</v>
+        <v>34.7</v>
       </c>
       <c r="E3" t="n">
-        <v>23.3</v>
+        <v>24.4</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -569,16 +569,16 @@
         <v>1051</v>
       </c>
       <c r="B4" t="n">
-        <v>97</v>
+        <v>902</v>
       </c>
       <c r="C4" t="n">
-        <v>70</v>
+        <v>57.3</v>
       </c>
       <c r="D4" t="n">
-        <v>42.1</v>
+        <v>27</v>
       </c>
       <c r="E4" t="n">
-        <v>27.9</v>
+        <v>30.2</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -591,16 +591,16 @@
         <v>1052</v>
       </c>
       <c r="B5" t="n">
-        <v>111</v>
+        <v>923</v>
       </c>
       <c r="C5" t="n">
-        <v>63.6</v>
+        <v>54.3</v>
       </c>
       <c r="D5" t="n">
-        <v>44.8</v>
+        <v>32.8</v>
       </c>
       <c r="E5" t="n">
-        <v>18.9</v>
+        <v>21.5</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -619,7 +619,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -686,11 +686,6 @@
           <t>Occupational Therapy</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>no graduates in extract?? check with Quality</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -698,9 +693,14 @@
           <t>Pharmacy</t>
         </is>
       </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Y?</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>no graduates in extract?? check</t>
+          <t>Elf count small. check</t>
         </is>
       </c>
     </row>
@@ -710,9 +710,14 @@
           <t>Physiotherapy</t>
         </is>
       </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Y?</t>
+        </is>
+      </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>no graduates in extract?? check</t>
+          <t>Elf count small. check</t>
         </is>
       </c>
     </row>
@@ -722,11 +727,6 @@
           <t>Social Work</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>no graduates in extract?? check</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -734,19 +734,6 @@
           <t>Nursing and Care</t>
         </is>
       </c>
-      <c r="B7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>two-year programme</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -754,19 +741,6 @@
           <t>Midwifery</t>
         </is>
       </c>
-      <c r="B8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>two-year programme</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -774,17 +748,11 @@
           <t>Education Studies</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>two-year programme</t>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>(other four not started)</t>
         </is>
       </c>
     </row>
@@ -802,7 +770,7 @@
   <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="60" customWidth="1" min="1" max="1"/>
+    <col width="56" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -828,7 +796,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Check why only SWE has graduates in the extract. Record system issue or genuine?</t>
+          <t>Fill programme rows from the csv</t>
         </is>
       </c>
     </row>
